--- a/reports/2026-08_月次実績報告/excel/第51期下期水産部部門別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期水産部部門別実績.xlsx
@@ -10516,7 +10516,10 @@
         <v/>
       </c>
       <c r="J114" s="92" t="n"/>
-      <c r="K114" s="93" t="n"/>
+      <c r="K114" s="92">
+        <f>SUM(E114:J114)</f>
+        <v/>
+      </c>
       <c r="L114" s="71">
         <f>全体!L114-機械!L114</f>
         <v/>
@@ -10537,7 +10540,10 @@
         <v/>
       </c>
       <c r="Q114" s="94" t="n"/>
-      <c r="R114" s="85" t="n"/>
+      <c r="R114" s="94">
+        <f>SUM(L114:Q114)</f>
+        <v/>
+      </c>
       <c r="S114" s="149" t="n"/>
       <c r="T114" s="149" t="n"/>
       <c r="U114" s="149" t="n"/>
@@ -12966,7 +12972,10 @@
         <v/>
       </c>
       <c r="J147" s="20" t="n"/>
-      <c r="K147" s="85" t="n"/>
+      <c r="K147" s="20">
+        <f>SUM(E147:J147)</f>
+        <v/>
+      </c>
       <c r="L147" s="20">
         <f>L114-L31</f>
         <v/>
@@ -21216,7 +21225,10 @@
         <v>0</v>
       </c>
       <c r="J114" s="84" t="n"/>
-      <c r="K114" s="85" t="n"/>
+      <c r="K114" s="84">
+        <f>SUM(E114:J114)</f>
+        <v/>
+      </c>
       <c r="L114" s="84" t="n">
         <v>0</v>
       </c>
@@ -21227,7 +21239,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="84" t="n"/>
-      <c r="R114" s="85" t="n"/>
+      <c r="R114" s="84">
+        <f>SUM(L114:Q114)</f>
+        <v/>
+      </c>
       <c r="S114" s="149" t="n"/>
       <c r="T114" s="149" t="n"/>
       <c r="U114" s="149" t="n"/>
@@ -23704,7 +23719,10 @@
         <f>J114-J31</f>
         <v/>
       </c>
-      <c r="K147" s="85" t="n"/>
+      <c r="K147" s="4">
+        <f>SUM(E147:J147)</f>
+        <v/>
+      </c>
       <c r="L147" s="20">
         <f>L114-L31</f>
         <v/>
@@ -32604,7 +32622,10 @@
         <v>0</v>
       </c>
       <c r="J114" s="84" t="n"/>
-      <c r="K114" s="85" t="n"/>
+      <c r="K114" s="84">
+        <f>SUM(E114:J114)</f>
+        <v/>
+      </c>
       <c r="L114" s="84" t="n">
         <v>0</v>
       </c>
@@ -32615,7 +32636,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="84" t="n"/>
-      <c r="R114" s="85" t="n"/>
+      <c r="R114" s="84">
+        <f>SUM(L114:Q114)</f>
+        <v/>
+      </c>
       <c r="S114" s="149" t="n"/>
       <c r="T114" s="149" t="n"/>
       <c r="U114" s="149" t="n"/>
@@ -35075,7 +35099,10 @@
         <v/>
       </c>
       <c r="J147" s="20" t="n"/>
-      <c r="K147" s="85" t="n"/>
+      <c r="K147" s="20">
+        <f>SUM(E147:J147)</f>
+        <v/>
+      </c>
       <c r="L147" s="20">
         <f>L114-L31</f>
         <v/>
